--- a/code/data/combined/cmb+pelg+jmul-w0wacdm-free.xlsx
+++ b/code/data/combined/cmb+pelg+jmul-w0wacdm-free.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -482,31 +482,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39309903.707763</v>
+        <v>44521433.80206043</v>
       </c>
       <c r="C2" t="n">
-        <v>-134472624.564042</v>
+        <v>-148871301.4438304</v>
       </c>
       <c r="D2" t="n">
-        <v>40498344.88594885</v>
+        <v>46542703.77037866</v>
       </c>
       <c r="E2" t="n">
-        <v>-328826.7713288474</v>
+        <v>-386670.9606377032</v>
       </c>
       <c r="F2" t="n">
-        <v>-1339492.47369304</v>
+        <v>-1342250.050849529</v>
       </c>
       <c r="G2" t="n">
-        <v>879085.3644684952</v>
+        <v>1047468.985227072</v>
       </c>
       <c r="H2" t="n">
-        <v>-2582307.606632393</v>
+        <v>-2937963.258048081</v>
       </c>
       <c r="I2" t="n">
-        <v>6316971.330598816</v>
+        <v>7237554.667721449</v>
       </c>
       <c r="J2" t="n">
-        <v>1706714.956497781</v>
+        <v>1955924.070145847</v>
       </c>
     </row>
     <row r="3">
@@ -516,31 +516,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-134472624.5718243</v>
+        <v>-148871301.451523</v>
       </c>
       <c r="C3" t="n">
-        <v>887787810.5080322</v>
+        <v>895579660.6372663</v>
       </c>
       <c r="D3" t="n">
-        <v>-89236526.52844189</v>
+        <v>-111670939.5379159</v>
       </c>
       <c r="E3" t="n">
-        <v>15622280.8261094</v>
+        <v>16225352.7556672</v>
       </c>
       <c r="F3" t="n">
-        <v>6725763.597818963</v>
+        <v>6678773.488248703</v>
       </c>
       <c r="G3" t="n">
-        <v>-3830849.072159663</v>
+        <v>-4434906.740593434</v>
       </c>
       <c r="H3" t="n">
-        <v>7955227.511256446</v>
+        <v>8983941.631022112</v>
       </c>
       <c r="I3" t="n">
-        <v>-24732459.78159483</v>
+        <v>-27603638.23985098</v>
       </c>
       <c r="J3" t="n">
-        <v>-6672907.634904982</v>
+        <v>-7452078.231360553</v>
       </c>
     </row>
     <row r="4">
@@ -550,31 +550,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40498344.8849516</v>
+        <v>46542703.76961052</v>
       </c>
       <c r="C4" t="n">
-        <v>-89236526.51647609</v>
+        <v>-111670939.5269969</v>
       </c>
       <c r="D4" t="n">
-        <v>48990351.07167155</v>
+        <v>55092578.15328556</v>
       </c>
       <c r="E4" t="n">
-        <v>921795.3902829071</v>
+        <v>834589.4581368262</v>
       </c>
       <c r="F4" t="n">
-        <v>-954046.0477920935</v>
+        <v>-978168.1869889036</v>
       </c>
       <c r="G4" t="n">
-        <v>971974.4850336568</v>
+        <v>1153342.968694657</v>
       </c>
       <c r="H4" t="n">
-        <v>-2835900.031918642</v>
+        <v>-3237876.534326999</v>
       </c>
       <c r="I4" t="n">
-        <v>6531917.673926622</v>
+        <v>7573296.416856018</v>
       </c>
       <c r="J4" t="n">
-        <v>1765079.687101024</v>
+        <v>2046725.739497366</v>
       </c>
     </row>
     <row r="5">
@@ -584,31 +584,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-328826.7715520093</v>
+        <v>-386670.960974264</v>
       </c>
       <c r="C5" t="n">
-        <v>15622280.82662977</v>
+        <v>16225352.7566426</v>
       </c>
       <c r="D5" t="n">
-        <v>921795.3900042443</v>
+        <v>834589.4577499289</v>
       </c>
       <c r="E5" t="n">
-        <v>1030767.84639808</v>
+        <v>1117992.60110274</v>
       </c>
       <c r="F5" t="n">
-        <v>29917.84074763138</v>
+        <v>48796.32697184238</v>
       </c>
       <c r="G5" t="n">
-        <v>-77271.80251846074</v>
+        <v>-84827.69390427305</v>
       </c>
       <c r="H5" t="n">
-        <v>-6239.261660063059</v>
+        <v>-5472.509787448573</v>
       </c>
       <c r="I5" t="n">
-        <v>-271712.1492873791</v>
+        <v>-302109.0741883367</v>
       </c>
       <c r="J5" t="n">
-        <v>-72255.40760429266</v>
+        <v>-80513.05114790014</v>
       </c>
     </row>
     <row r="6">
@@ -618,31 +618,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1339492.473758571</v>
+        <v>-1342250.05087943</v>
       </c>
       <c r="C6" t="n">
-        <v>6725763.598136184</v>
+        <v>6678773.488430323</v>
       </c>
       <c r="D6" t="n">
-        <v>-954046.047854281</v>
+        <v>-978168.1870133573</v>
       </c>
       <c r="E6" t="n">
-        <v>29917.84075332552</v>
+        <v>48796.32697562304</v>
       </c>
       <c r="F6" t="n">
-        <v>637642.8265060139</v>
+        <v>638620.3949295635</v>
       </c>
       <c r="G6" t="n">
-        <v>103899.4427322654</v>
+        <v>102682.2695605452</v>
       </c>
       <c r="H6" t="n">
-        <v>42096.5870016859</v>
+        <v>41197.21617230917</v>
       </c>
       <c r="I6" t="n">
-        <v>-13611.52148475828</v>
+        <v>-17493.24470678075</v>
       </c>
       <c r="J6" t="n">
-        <v>-2370.838423332611</v>
+        <v>-3409.690510896983</v>
       </c>
     </row>
     <row r="7">
@@ -652,31 +652,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>879085.3644680337</v>
+        <v>1047468.985259324</v>
       </c>
       <c r="C7" t="n">
-        <v>-3830849.071849243</v>
+        <v>-4434906.740414117</v>
       </c>
       <c r="D7" t="n">
-        <v>971974.485072365</v>
+        <v>1153342.96875891</v>
       </c>
       <c r="E7" t="n">
-        <v>-77271.80250938085</v>
+        <v>-84827.69389247944</v>
       </c>
       <c r="F7" t="n">
-        <v>103899.44273507</v>
+        <v>102682.2695619044</v>
       </c>
       <c r="G7" t="n">
-        <v>66769.24939209828</v>
+        <v>72669.37597258639</v>
       </c>
       <c r="H7" t="n">
-        <v>-71180.87004958937</v>
+        <v>-82394.7338980802</v>
       </c>
       <c r="I7" t="n">
-        <v>228801.4399395029</v>
+        <v>260147.3115889</v>
       </c>
       <c r="J7" t="n">
-        <v>62469.54455054675</v>
+        <v>70959.19992923018</v>
       </c>
     </row>
     <row r="8">
@@ -686,31 +686,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-2582307.606611361</v>
+        <v>-2937963.258034681</v>
       </c>
       <c r="C8" t="n">
-        <v>7955227.510628859</v>
+        <v>8983941.630433321</v>
       </c>
       <c r="D8" t="n">
-        <v>-2835900.031966532</v>
+        <v>-3237876.534366698</v>
       </c>
       <c r="E8" t="n">
-        <v>-6239.261676758259</v>
+        <v>-5472.509811528605</v>
       </c>
       <c r="F8" t="n">
-        <v>42096.58699721137</v>
+        <v>41197.21617033783</v>
       </c>
       <c r="G8" t="n">
-        <v>-71180.8700487829</v>
+        <v>-82394.73389530022</v>
       </c>
       <c r="H8" t="n">
-        <v>178514.0622268772</v>
+        <v>202848.6947778672</v>
       </c>
       <c r="I8" t="n">
-        <v>-437183.7236517405</v>
+        <v>-499155.3293706121</v>
       </c>
       <c r="J8" t="n">
-        <v>-118210.0408313333</v>
+        <v>-134981.6762909128</v>
       </c>
     </row>
     <row r="9">
@@ -720,31 +720,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6316971.330622019</v>
+        <v>7237554.667818638</v>
       </c>
       <c r="C9" t="n">
-        <v>-24732459.78016954</v>
+        <v>-27603638.23873176</v>
       </c>
       <c r="D9" t="n">
-        <v>6531917.674144605</v>
+        <v>7573296.417107358</v>
       </c>
       <c r="E9" t="n">
-        <v>-271712.1492446244</v>
+        <v>-302109.0741273772</v>
       </c>
       <c r="F9" t="n">
-        <v>-13611.52147127296</v>
+        <v>-17493.24470035039</v>
       </c>
       <c r="G9" t="n">
-        <v>228801.4399405641</v>
+        <v>260147.3115864562</v>
       </c>
       <c r="H9" t="n">
-        <v>-437183.7236574891</v>
+        <v>-499155.3293799964</v>
       </c>
       <c r="I9" t="n">
-        <v>1195073.790116115</v>
+        <v>1363175.57972181</v>
       </c>
       <c r="J9" t="n">
-        <v>323623.1395212704</v>
+        <v>369137.6883407279</v>
       </c>
     </row>
     <row r="10">
@@ -754,31 +754,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1706714.956503738</v>
+        <v>1955924.070172493</v>
       </c>
       <c r="C10" t="n">
-        <v>-6672907.634516569</v>
+        <v>-7452078.231059886</v>
       </c>
       <c r="D10" t="n">
-        <v>1765079.687159867</v>
+        <v>2046725.73956556</v>
       </c>
       <c r="E10" t="n">
-        <v>-72255.40759268288</v>
+        <v>-80513.05113130804</v>
       </c>
       <c r="F10" t="n">
-        <v>-2370.838419672637</v>
+        <v>-3409.69050915525</v>
       </c>
       <c r="G10" t="n">
-        <v>62469.5445508216</v>
+        <v>70959.19992857665</v>
       </c>
       <c r="H10" t="n">
-        <v>-118210.0408328697</v>
+        <v>-134981.6762934773</v>
       </c>
       <c r="I10" t="n">
-        <v>323623.1395212045</v>
+        <v>369137.6883407779</v>
       </c>
       <c r="J10" t="n">
-        <v>87740.08077146826</v>
+        <v>100063.4777243654</v>
       </c>
     </row>
   </sheetData>

--- a/code/data/combined/cmb+pelg+jmul-w0wacdm-free.xlsx
+++ b/code/data/combined/cmb+pelg+jmul-w0wacdm-free.xlsx
@@ -482,31 +482,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44521433.80206043</v>
+        <v>43671284.56377615</v>
       </c>
       <c r="C2" t="n">
-        <v>-148871301.4438304</v>
+        <v>-146032037.9417794</v>
       </c>
       <c r="D2" t="n">
-        <v>46542703.77037866</v>
+        <v>45623756.25760421</v>
       </c>
       <c r="E2" t="n">
-        <v>-386670.9606377032</v>
+        <v>-379416.1538402764</v>
       </c>
       <c r="F2" t="n">
-        <v>-1342250.050849529</v>
+        <v>-1334633.657322105</v>
       </c>
       <c r="G2" t="n">
-        <v>1047468.985227072</v>
+        <v>1020578.406227055</v>
       </c>
       <c r="H2" t="n">
-        <v>-2937963.258048081</v>
+        <v>-2878123.168614196</v>
       </c>
       <c r="I2" t="n">
-        <v>7237554.667721449</v>
+        <v>7086496.159433469</v>
       </c>
       <c r="J2" t="n">
-        <v>1955924.070145847</v>
+        <v>1915014.279129845</v>
       </c>
     </row>
     <row r="3">
@@ -516,31 +516,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-148871301.451523</v>
+        <v>-146032037.9295744</v>
       </c>
       <c r="C3" t="n">
-        <v>895579660.6372663</v>
+        <v>876730590.4647939</v>
       </c>
       <c r="D3" t="n">
-        <v>-111670939.5379159</v>
+        <v>-109841979.5764368</v>
       </c>
       <c r="E3" t="n">
-        <v>16225352.7556672</v>
+        <v>15993899.88984527</v>
       </c>
       <c r="F3" t="n">
-        <v>6678773.488248703</v>
+        <v>6606462.467018127</v>
       </c>
       <c r="G3" t="n">
-        <v>-4434906.740593434</v>
+        <v>-4341449.679200747</v>
       </c>
       <c r="H3" t="n">
-        <v>8983941.631022112</v>
+        <v>8805594.642663095</v>
       </c>
       <c r="I3" t="n">
-        <v>-27603638.23985098</v>
+        <v>-27073703.00998607</v>
       </c>
       <c r="J3" t="n">
-        <v>-7452078.231360553</v>
+        <v>-7308700.567527838</v>
       </c>
     </row>
     <row r="4">
@@ -550,31 +550,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>46542703.76961052</v>
+        <v>45623756.25894078</v>
       </c>
       <c r="C4" t="n">
-        <v>-111670939.5269969</v>
+        <v>-109841979.5941505</v>
       </c>
       <c r="D4" t="n">
-        <v>55092578.15328556</v>
+        <v>53932634.0447951</v>
       </c>
       <c r="E4" t="n">
-        <v>834589.4581368262</v>
+        <v>816073.8811710108</v>
       </c>
       <c r="F4" t="n">
-        <v>-978168.1869889036</v>
+        <v>-974232.5062977787</v>
       </c>
       <c r="G4" t="n">
-        <v>1153342.968694657</v>
+        <v>1124804.266837257</v>
       </c>
       <c r="H4" t="n">
-        <v>-3237876.534326999</v>
+        <v>-3170427.902261901</v>
       </c>
       <c r="I4" t="n">
-        <v>7573296.416856018</v>
+        <v>7413155.218172072</v>
       </c>
       <c r="J4" t="n">
-        <v>2046725.739497366</v>
+        <v>2003334.661481295</v>
       </c>
     </row>
     <row r="5">
@@ -584,31 +584,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-386670.960974264</v>
+        <v>-379416.1533401931</v>
       </c>
       <c r="C5" t="n">
-        <v>16225352.7566426</v>
+        <v>15993899.88842345</v>
       </c>
       <c r="D5" t="n">
-        <v>834589.4577499289</v>
+        <v>816073.8817348779</v>
       </c>
       <c r="E5" t="n">
-        <v>1117992.60110274</v>
+        <v>1110110.422543833</v>
       </c>
       <c r="F5" t="n">
-        <v>48796.32697184238</v>
+        <v>48716.74949178952</v>
       </c>
       <c r="G5" t="n">
-        <v>-84827.69390427305</v>
+        <v>-84279.01036371439</v>
       </c>
       <c r="H5" t="n">
-        <v>-5472.509787448573</v>
+        <v>-5348.626913812055</v>
       </c>
       <c r="I5" t="n">
-        <v>-302109.0741883367</v>
+        <v>-299688.0398270841</v>
       </c>
       <c r="J5" t="n">
-        <v>-80513.05114790014</v>
+        <v>-79864.86053413636</v>
       </c>
     </row>
     <row r="6">
@@ -618,31 +618,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1342250.05087943</v>
+        <v>-1334633.657179013</v>
       </c>
       <c r="C6" t="n">
-        <v>6678773.488430323</v>
+        <v>6606462.466744252</v>
       </c>
       <c r="D6" t="n">
-        <v>-978168.1870133573</v>
+        <v>-974232.506121267</v>
       </c>
       <c r="E6" t="n">
-        <v>48796.32697562304</v>
+        <v>48716.74949697322</v>
       </c>
       <c r="F6" t="n">
-        <v>638620.3949295635</v>
+        <v>634464.500096424</v>
       </c>
       <c r="G6" t="n">
-        <v>102682.2695605452</v>
+        <v>102551.1391867935</v>
       </c>
       <c r="H6" t="n">
-        <v>41197.21617230917</v>
+        <v>40814.74904866835</v>
       </c>
       <c r="I6" t="n">
-        <v>-17493.24470678075</v>
+        <v>-16443.53978504139</v>
       </c>
       <c r="J6" t="n">
-        <v>-3409.690510896983</v>
+        <v>-3118.524959346611</v>
       </c>
     </row>
     <row r="7">
@@ -652,31 +652,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1047468.985259324</v>
+        <v>1020578.406209487</v>
       </c>
       <c r="C7" t="n">
-        <v>-4434906.740414117</v>
+        <v>-4341449.679499944</v>
       </c>
       <c r="D7" t="n">
-        <v>1153342.96875891</v>
+        <v>1124804.266779163</v>
       </c>
       <c r="E7" t="n">
-        <v>-84827.69389247944</v>
+        <v>-84279.01037808358</v>
       </c>
       <c r="F7" t="n">
-        <v>102682.2695619044</v>
+        <v>102551.1391828868</v>
       </c>
       <c r="G7" t="n">
-        <v>72669.37597258639</v>
+        <v>71761.94659210474</v>
       </c>
       <c r="H7" t="n">
-        <v>-82394.7338980802</v>
+        <v>-80510.04119578392</v>
       </c>
       <c r="I7" t="n">
-        <v>260147.3115889</v>
+        <v>255272.1080305171</v>
       </c>
       <c r="J7" t="n">
-        <v>70959.19992923018</v>
+        <v>69639.76283093923</v>
       </c>
     </row>
     <row r="8">
@@ -686,31 +686,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-2937963.258034681</v>
+        <v>-2878123.16864571</v>
       </c>
       <c r="C8" t="n">
-        <v>8983941.630433321</v>
+        <v>8805594.643594814</v>
       </c>
       <c r="D8" t="n">
-        <v>-3237876.534366698</v>
+        <v>-3170427.902205629</v>
       </c>
       <c r="E8" t="n">
-        <v>-5472.509811528605</v>
+        <v>-5348.626878921499</v>
       </c>
       <c r="F8" t="n">
-        <v>41197.21617033783</v>
+        <v>40814.74905892376</v>
       </c>
       <c r="G8" t="n">
-        <v>-82394.73389530022</v>
+        <v>-80510.04119790929</v>
       </c>
       <c r="H8" t="n">
-        <v>202848.6947778672</v>
+        <v>198571.6201001841</v>
       </c>
       <c r="I8" t="n">
-        <v>-499155.3293706121</v>
+        <v>-488592.0571662035</v>
       </c>
       <c r="J8" t="n">
-        <v>-134981.6762909128</v>
+        <v>-132120.5431112949</v>
       </c>
     </row>
     <row r="9">
@@ -720,31 +720,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7237554.667818638</v>
+        <v>7086496.159339867</v>
       </c>
       <c r="C9" t="n">
-        <v>-27603638.23873176</v>
+        <v>-27073703.01180466</v>
       </c>
       <c r="D9" t="n">
-        <v>7573296.417107358</v>
+        <v>7413155.217837711</v>
       </c>
       <c r="E9" t="n">
-        <v>-302109.0741273772</v>
+        <v>-299688.0399122992</v>
       </c>
       <c r="F9" t="n">
-        <v>-17493.24470035039</v>
+        <v>-16443.53980843446</v>
       </c>
       <c r="G9" t="n">
-        <v>260147.3115864562</v>
+        <v>255272.1080308288</v>
       </c>
       <c r="H9" t="n">
-        <v>-499155.3293799964</v>
+        <v>-488592.0571543233</v>
       </c>
       <c r="I9" t="n">
-        <v>1363175.57972181</v>
+        <v>1336089.047722255</v>
       </c>
       <c r="J9" t="n">
-        <v>369137.6883407279</v>
+        <v>361803.527659978</v>
       </c>
     </row>
     <row r="10">
@@ -754,31 +754,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1955924.070172493</v>
+        <v>1915014.27910465</v>
       </c>
       <c r="C10" t="n">
-        <v>-7452078.231059886</v>
+        <v>-7308700.568016921</v>
       </c>
       <c r="D10" t="n">
-        <v>2046725.73956556</v>
+        <v>2003334.66139147</v>
       </c>
       <c r="E10" t="n">
-        <v>-80513.05113130804</v>
+        <v>-79864.86055727224</v>
       </c>
       <c r="F10" t="n">
-        <v>-3409.69050915525</v>
+        <v>-3118.524965675056</v>
       </c>
       <c r="G10" t="n">
-        <v>70959.19992857665</v>
+        <v>69639.76283102774</v>
       </c>
       <c r="H10" t="n">
-        <v>-134981.6762934773</v>
+        <v>-132120.5431080923</v>
       </c>
       <c r="I10" t="n">
-        <v>369137.6883407779</v>
+        <v>361803.5276600023</v>
       </c>
       <c r="J10" t="n">
-        <v>100063.4777243654</v>
+        <v>98077.60200948606</v>
       </c>
     </row>
   </sheetData>
